--- a/docs/planning/1. Sprint Timeplan - Tsering Lhamo Anodunkhartsang.xlsx
+++ b/docs/planning/1. Sprint Timeplan - Tsering Lhamo Anodunkhartsang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/t.anodunkhartsang/projects/sovereign-ai-agent/docs/planning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27C3B15-1FDF-234E-8D06-2D6329059FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA9CB16-59E5-EB48-A3AF-C5FD56C38169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="69180" yWindow="9820" windowWidth="30240" windowHeight="17580" xr2:uid="{AB7B3E1D-6C2A-9542-8379-0F3DD31EEDCF}"/>
+    <workbookView xWindow="68800" yWindow="9820" windowWidth="30240" windowHeight="17580" xr2:uid="{AB7B3E1D-6C2A-9542-8379-0F3DD31EEDCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeplan" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="67">
   <si>
     <t>OOO</t>
   </si>
@@ -1404,186 +1404,186 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2231,228 +2231,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="105" t="s">
+      <c r="D1" s="78"/>
+      <c r="E1" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
-      <c r="AL1" s="105"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
+      <c r="AO1" s="79"/>
+      <c r="AP1" s="79"/>
+      <c r="AQ1" s="79"/>
+      <c r="AR1" s="79"/>
     </row>
     <row r="2" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="72" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="72" t="s">
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
+      <c r="U2" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72"/>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="72"/>
-      <c r="AO2" s="72"/>
-      <c r="AP2" s="72"/>
-      <c r="AQ2" s="72"/>
-      <c r="AR2" s="72"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="91"/>
+      <c r="X2" s="91"/>
+      <c r="Y2" s="91"/>
+      <c r="Z2" s="91"/>
+      <c r="AA2" s="91"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="91"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="91"/>
+      <c r="AQ2" s="91"/>
+      <c r="AR2" s="91"/>
     </row>
     <row r="3" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="101"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="75" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="61" t="s">
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="64" t="s">
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="117"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="117"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="118"/>
+      <c r="U3" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="64" t="s">
+      <c r="V3" s="107"/>
+      <c r="W3" s="107"/>
+      <c r="X3" s="107"/>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="107"/>
+      <c r="AA3" s="107"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="64" t="s">
+      <c r="AD3" s="107"/>
+      <c r="AE3" s="107"/>
+      <c r="AF3" s="107"/>
+      <c r="AG3" s="107"/>
+      <c r="AH3" s="107"/>
+      <c r="AI3" s="107"/>
+      <c r="AJ3" s="108"/>
+      <c r="AK3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="AL3" s="68"/>
-      <c r="AM3" s="68"/>
-      <c r="AN3" s="68"/>
-      <c r="AO3" s="68"/>
-      <c r="AP3" s="68"/>
-      <c r="AQ3" s="68"/>
-      <c r="AR3" s="69"/>
+      <c r="AL3" s="78"/>
+      <c r="AM3" s="78"/>
+      <c r="AN3" s="78"/>
+      <c r="AO3" s="78"/>
+      <c r="AP3" s="78"/>
+      <c r="AQ3" s="78"/>
+      <c r="AR3" s="111"/>
     </row>
     <row r="4" spans="1:44" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="75"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="58" t="s">
+      <c r="D4" s="100"/>
+      <c r="E4" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="55" t="s">
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="58" t="s">
+      <c r="N4" s="114"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="V4" s="59"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
-      <c r="Z4" s="59"/>
-      <c r="AA4" s="59"/>
-      <c r="AB4" s="60"/>
-      <c r="AC4" s="58" t="s">
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
+      <c r="Z4" s="109"/>
+      <c r="AA4" s="109"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="AD4" s="59"/>
-      <c r="AE4" s="59"/>
-      <c r="AF4" s="59"/>
-      <c r="AG4" s="59"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="60"/>
-      <c r="AK4" s="58" t="s">
+      <c r="AD4" s="109"/>
+      <c r="AE4" s="109"/>
+      <c r="AF4" s="109"/>
+      <c r="AG4" s="109"/>
+      <c r="AH4" s="109"/>
+      <c r="AI4" s="109"/>
+      <c r="AJ4" s="110"/>
+      <c r="AK4" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="AL4" s="70"/>
-      <c r="AM4" s="70"/>
-      <c r="AN4" s="70"/>
-      <c r="AO4" s="70"/>
-      <c r="AP4" s="70"/>
-      <c r="AQ4" s="70"/>
-      <c r="AR4" s="71"/>
+      <c r="AL4" s="95"/>
+      <c r="AM4" s="95"/>
+      <c r="AN4" s="95"/>
+      <c r="AO4" s="95"/>
+      <c r="AP4" s="95"/>
+      <c r="AQ4" s="95"/>
+      <c r="AR4" s="112"/>
     </row>
     <row r="5" spans="1:44" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="96" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="21" t="s">
@@ -2506,8 +2506,8 @@
       <c r="AR5" s="18"/>
     </row>
     <row r="6" spans="1:44" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="83"/>
-      <c r="B6" s="78"/>
+      <c r="A6" s="101"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="22" t="s">
         <v>2</v>
       </c>
@@ -2559,8 +2559,8 @@
       <c r="AR6" s="6"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="83"/>
-      <c r="B7" s="79" t="s">
+      <c r="A7" s="101"/>
+      <c r="B7" s="97" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -2614,8 +2614,8 @@
       <c r="AR7" s="3"/>
     </row>
     <row r="8" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="23" t="s">
         <v>2</v>
       </c>
@@ -2667,10 +2667,10 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A9" s="115" t="s">
+      <c r="A9" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="103" t="s">
         <v>53</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -2724,8 +2724,8 @@
       <c r="AR9" s="53"/>
     </row>
     <row r="10" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="114"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="104"/>
       <c r="C10" s="23" t="s">
         <v>2</v>
       </c>
@@ -2777,8 +2777,8 @@
       <c r="AR10" s="50"/>
     </row>
     <row r="11" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="83"/>
-      <c r="B11" s="106" t="s">
+      <c r="A11" s="101"/>
+      <c r="B11" s="80" t="s">
         <v>52</v>
       </c>
       <c r="C11" s="21" t="s">
@@ -2838,8 +2838,8 @@
       </c>
     </row>
     <row r="12" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84"/>
-      <c r="B12" s="107"/>
+      <c r="A12" s="102"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="23" t="s">
         <v>2</v>
       </c>
@@ -2897,10 +2897,10 @@
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="55" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -2954,8 +2954,8 @@
       <c r="AR13" s="20"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="118"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="22" t="s">
         <v>2</v>
       </c>
@@ -3007,8 +3007,8 @@
       <c r="AR14" s="6"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A15" s="88"/>
-      <c r="B15" s="119" t="s">
+      <c r="A15" s="89"/>
+      <c r="B15" s="58" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -3062,8 +3062,8 @@
       <c r="AR15" s="3"/>
     </row>
     <row r="16" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="89"/>
-      <c r="B16" s="86"/>
+      <c r="A16" s="90"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="23" t="s">
         <v>2</v>
       </c>
@@ -3115,10 +3115,10 @@
       <c r="AR16" s="15"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="55" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="24" t="s">
@@ -3172,8 +3172,8 @@
       <c r="AR17" s="20"/>
     </row>
     <row r="18" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="74"/>
-      <c r="B18" s="86"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="23" t="s">
         <v>2</v>
       </c>
@@ -3225,10 +3225,10 @@
       <c r="AR18" s="15"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="55" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="24" t="s">
@@ -3284,8 +3284,8 @@
       <c r="AR19" s="20"/>
     </row>
     <row r="20" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74"/>
-      <c r="B20" s="86"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="23" t="s">
         <v>2</v>
       </c>
@@ -3339,10 +3339,10 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="55" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="25" t="s">
@@ -3398,8 +3398,8 @@
       <c r="AR21" s="20"/>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A22" s="90"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="62"/>
+      <c r="B22" s="56"/>
       <c r="C22" s="22" t="s">
         <v>2</v>
       </c>
@@ -3453,8 +3453,8 @@
       <c r="AR22" s="6"/>
     </row>
     <row r="23" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="90"/>
-      <c r="B23" s="92" t="s">
+      <c r="A23" s="62"/>
+      <c r="B23" s="87" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -3508,8 +3508,8 @@
       <c r="AR23" s="3"/>
     </row>
     <row r="24" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="91"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="23" t="s">
         <v>2</v>
       </c>
@@ -3561,10 +3561,10 @@
       <c r="AR24" s="15"/>
     </row>
     <row r="25" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="55" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="24" t="s">
@@ -3620,8 +3620,8 @@
       <c r="AR25" s="20"/>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A26" s="90"/>
-      <c r="B26" s="78"/>
+      <c r="A26" s="62"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="22" t="s">
         <v>2</v>
       </c>
@@ -3675,8 +3675,8 @@
       <c r="AR26" s="6"/>
     </row>
     <row r="27" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="90"/>
-      <c r="B27" s="92" t="s">
+      <c r="A27" s="62"/>
+      <c r="B27" s="87" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="21" t="s">
@@ -3732,8 +3732,8 @@
       <c r="AR27" s="3"/>
     </row>
     <row r="28" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="91"/>
-      <c r="B28" s="86"/>
+      <c r="A28" s="63"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="23" t="s">
         <v>2</v>
       </c>
@@ -3787,10 +3787,10 @@
       <c r="AR28" s="15"/>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="55" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="24" t="s">
@@ -3844,8 +3844,8 @@
       <c r="AR29" s="20"/>
     </row>
     <row r="30" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74"/>
-      <c r="B30" s="86"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="23" t="s">
         <v>2</v>
       </c>
@@ -3897,10 +3897,10 @@
       <c r="AR30" s="15"/>
     </row>
     <row r="31" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="55" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="24" t="s">
@@ -3956,8 +3956,8 @@
       <c r="AR31" s="20"/>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A32" s="90"/>
-      <c r="B32" s="78"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="22" t="s">
         <v>2</v>
       </c>
@@ -4011,8 +4011,8 @@
       <c r="AR32" s="6"/>
     </row>
     <row r="33" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="62"/>
+      <c r="B33" s="87" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="21" t="s">
@@ -4068,8 +4068,8 @@
       <c r="AR33" s="3"/>
     </row>
     <row r="34" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="91"/>
-      <c r="B34" s="86"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="59"/>
       <c r="C34" s="23" t="s">
         <v>2</v>
       </c>
@@ -4123,10 +4123,10 @@
       <c r="AR34" s="15"/>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="55" t="s">
         <v>28</v>
       </c>
       <c r="C35" s="24" t="s">
@@ -4182,8 +4182,8 @@
       <c r="AR35" s="20"/>
     </row>
     <row r="36" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="74"/>
-      <c r="B36" s="86"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="23" t="s">
         <v>2</v>
       </c>
@@ -4237,10 +4237,10 @@
       <c r="AR36" s="15"/>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="55" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="24" t="s">
@@ -4296,8 +4296,8 @@
       <c r="AR37" s="20"/>
     </row>
     <row r="38" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="74"/>
-      <c r="B38" s="86"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="59"/>
       <c r="C38" s="23" t="s">
         <v>2</v>
       </c>
@@ -4351,10 +4351,10 @@
       <c r="AR38" s="15"/>
     </row>
     <row r="39" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="55" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="24" t="s">
@@ -4414,14 +4414,14 @@
       <c r="AR39" s="20"/>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A40" s="90"/>
-      <c r="B40" s="78"/>
+      <c r="A40" s="62"/>
+      <c r="B40" s="56"/>
       <c r="C40" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="30">
         <f t="shared" ref="D40" si="23">COUNTIF(E40:AR40,"i")/24</f>
-        <v>4.1666666666666664E-2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="5"/>
@@ -4458,17 +4458,23 @@
       <c r="AK40" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AL40" s="5"/>
-      <c r="AM40" s="5"/>
-      <c r="AN40" s="5"/>
+      <c r="AL40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN40" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
       <c r="AQ40" s="5"/>
       <c r="AR40" s="6"/>
     </row>
     <row r="41" spans="1:44" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="90"/>
-      <c r="B41" s="92" t="s">
+      <c r="A41" s="62"/>
+      <c r="B41" s="87" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="21" t="s">
@@ -4524,14 +4530,14 @@
       <c r="AR41" s="3"/>
     </row>
     <row r="42" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="91"/>
-      <c r="B42" s="86"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="29">
         <f t="shared" ref="D42" si="25">COUNTIF(E42:AR42,"i")/24</f>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="14"/>
@@ -4569,16 +4575,20 @@
       <c r="AL42" s="14"/>
       <c r="AM42" s="14"/>
       <c r="AN42" s="14"/>
-      <c r="AO42" s="14"/>
-      <c r="AP42" s="14"/>
+      <c r="AO42" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP42" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="AQ42" s="14"/>
       <c r="AR42" s="15"/>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="85" t="s">
+      <c r="B43" s="55" t="s">
         <v>32</v>
       </c>
       <c r="C43" s="24" t="s">
@@ -4632,14 +4642,14 @@
       <c r="AR43" s="20"/>
     </row>
     <row r="44" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="74"/>
-      <c r="B44" s="86"/>
+      <c r="A44" s="61"/>
+      <c r="B44" s="59"/>
       <c r="C44" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="30">
         <f t="shared" ref="D44" si="27">COUNTIF(E44:AR44,"i")/24</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="14"/>
@@ -4679,14 +4689,16 @@
       <c r="AN44" s="14"/>
       <c r="AO44" s="14"/>
       <c r="AP44" s="14"/>
-      <c r="AQ44" s="14"/>
+      <c r="AQ44" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="AR44" s="15"/>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="55" t="s">
         <v>51</v>
       </c>
       <c r="C45" s="24" t="s">
@@ -4740,14 +4752,14 @@
       </c>
     </row>
     <row r="46" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74"/>
-      <c r="B46" s="86"/>
+      <c r="A46" s="61"/>
+      <c r="B46" s="59"/>
       <c r="C46" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D46" s="29">
         <f t="shared" ref="D46" si="29">COUNTIF(E46:AR46,"i")/24</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="14"/>
@@ -4788,13 +4800,15 @@
       <c r="AO46" s="14"/>
       <c r="AP46" s="14"/>
       <c r="AQ46" s="14"/>
-      <c r="AR46" s="15"/>
+      <c r="AR46" s="15" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A47" s="108" t="s">
+      <c r="A47" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="108"/>
+      <c r="B47" s="82"/>
       <c r="C47" s="24" t="s">
         <v>15</v>
       </c>
@@ -4802,17 +4816,17 @@
         <f>SUMIF($C$5:$C$46,"should",$D$5:$D$46)</f>
         <v>1.3333333333333335</v>
       </c>
-      <c r="E47" s="93">
+      <c r="E47" s="66">
         <f>COUNTIF(E5:L46,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="F47" s="94"/>
-      <c r="G47" s="94"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="94"/>
-      <c r="J47" s="94"/>
-      <c r="K47" s="94"/>
-      <c r="L47" s="95"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="68"/>
       <c r="M47" s="33"/>
       <c r="N47" s="9"/>
       <c r="O47" s="9"/>
@@ -4821,61 +4835,61 @@
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
       <c r="T47" s="34"/>
-      <c r="U47" s="93">
+      <c r="U47" s="66">
         <f>COUNTIF(U5:AB46,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="V47" s="94"/>
-      <c r="W47" s="94"/>
-      <c r="X47" s="94"/>
-      <c r="Y47" s="94"/>
-      <c r="Z47" s="94"/>
-      <c r="AA47" s="94"/>
-      <c r="AB47" s="95"/>
-      <c r="AC47" s="93">
+      <c r="V47" s="67"/>
+      <c r="W47" s="67"/>
+      <c r="X47" s="67"/>
+      <c r="Y47" s="67"/>
+      <c r="Z47" s="67"/>
+      <c r="AA47" s="67"/>
+      <c r="AB47" s="68"/>
+      <c r="AC47" s="66">
         <f>COUNTIF(AC5:AJ46,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="AD47" s="94"/>
-      <c r="AE47" s="94"/>
-      <c r="AF47" s="94"/>
-      <c r="AG47" s="94"/>
-      <c r="AH47" s="94"/>
-      <c r="AI47" s="94"/>
-      <c r="AJ47" s="95"/>
-      <c r="AK47" s="93">
+      <c r="AD47" s="67"/>
+      <c r="AE47" s="67"/>
+      <c r="AF47" s="67"/>
+      <c r="AG47" s="67"/>
+      <c r="AH47" s="67"/>
+      <c r="AI47" s="67"/>
+      <c r="AJ47" s="68"/>
+      <c r="AK47" s="66">
         <f>COUNTIF(AK5:AR46,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="AL47" s="94"/>
-      <c r="AM47" s="94"/>
-      <c r="AN47" s="94"/>
-      <c r="AO47" s="94"/>
-      <c r="AP47" s="94"/>
-      <c r="AQ47" s="94"/>
-      <c r="AR47" s="95"/>
+      <c r="AL47" s="67"/>
+      <c r="AM47" s="67"/>
+      <c r="AN47" s="67"/>
+      <c r="AO47" s="67"/>
+      <c r="AP47" s="67"/>
+      <c r="AQ47" s="67"/>
+      <c r="AR47" s="68"/>
     </row>
     <row r="48" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="109"/>
-      <c r="B48" s="109"/>
+      <c r="A48" s="83"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D48" s="45">
         <f>SUMIF($C$5:$C$46,"is",$D$5:$D$46)</f>
-        <v>1.2083333333333333</v>
-      </c>
-      <c r="E48" s="110">
+        <v>1.5</v>
+      </c>
+      <c r="E48" s="84">
         <f>COUNTIF(E5:L46,"i")/24</f>
         <v>0.375</v>
       </c>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="112"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="85"/>
+      <c r="H48" s="85"/>
+      <c r="I48" s="85"/>
+      <c r="J48" s="85"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="86"/>
       <c r="M48" s="35"/>
       <c r="N48" s="36"/>
       <c r="O48" s="36"/>
@@ -4884,62 +4898,62 @@
       <c r="R48" s="36"/>
       <c r="S48" s="36"/>
       <c r="T48" s="37"/>
-      <c r="U48" s="96">
+      <c r="U48" s="69">
         <f>COUNTIF(U5:AB46,"i")/24</f>
         <v>0.375</v>
       </c>
-      <c r="V48" s="97"/>
-      <c r="W48" s="97"/>
-      <c r="X48" s="97"/>
-      <c r="Y48" s="97"/>
-      <c r="Z48" s="97"/>
-      <c r="AA48" s="97"/>
-      <c r="AB48" s="98"/>
-      <c r="AC48" s="96">
+      <c r="V48" s="70"/>
+      <c r="W48" s="70"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="70"/>
+      <c r="Z48" s="70"/>
+      <c r="AA48" s="70"/>
+      <c r="AB48" s="71"/>
+      <c r="AC48" s="69">
         <f>COUNTIF(AC5:AJ46,"i")/24</f>
         <v>0.375</v>
       </c>
-      <c r="AD48" s="97"/>
-      <c r="AE48" s="97"/>
-      <c r="AF48" s="97"/>
-      <c r="AG48" s="97"/>
-      <c r="AH48" s="97"/>
-      <c r="AI48" s="97"/>
-      <c r="AJ48" s="98"/>
-      <c r="AK48" s="96">
+      <c r="AD48" s="70"/>
+      <c r="AE48" s="70"/>
+      <c r="AF48" s="70"/>
+      <c r="AG48" s="70"/>
+      <c r="AH48" s="70"/>
+      <c r="AI48" s="70"/>
+      <c r="AJ48" s="71"/>
+      <c r="AK48" s="69">
         <f>COUNTIF(AK5:AR46,"i")/24</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="AL48" s="97"/>
-      <c r="AM48" s="97"/>
-      <c r="AN48" s="97"/>
-      <c r="AO48" s="97"/>
-      <c r="AP48" s="97"/>
-      <c r="AQ48" s="97"/>
-      <c r="AR48" s="98"/>
+        <v>0.375</v>
+      </c>
+      <c r="AL48" s="70"/>
+      <c r="AM48" s="70"/>
+      <c r="AN48" s="70"/>
+      <c r="AO48" s="70"/>
+      <c r="AP48" s="70"/>
+      <c r="AQ48" s="70"/>
+      <c r="AR48" s="71"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F49" s="116" t="s">
+      <c r="F49" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G49" s="117"/>
+      <c r="G49" s="65"/>
       <c r="I49" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="116" t="s">
+      <c r="J49" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="K49" s="117"/>
+      <c r="K49" s="65"/>
     </row>
     <row r="50" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:11" ht="19" x14ac:dyDescent="0.25">
-      <c r="A51" s="99" t="s">
+      <c r="A51" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="100"/>
+      <c r="B51" s="73"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="46" t="s">
@@ -4959,19 +4973,34 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="AC47:AJ47"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="M4:T4"/>
+    <mergeCell ref="U4:AB4"/>
+    <mergeCell ref="M3:T3"/>
+    <mergeCell ref="U3:AB3"/>
+    <mergeCell ref="M2:T2"/>
+    <mergeCell ref="AC3:AJ3"/>
+    <mergeCell ref="AC4:AJ4"/>
+    <mergeCell ref="AK3:AR3"/>
+    <mergeCell ref="AK4:AR4"/>
+    <mergeCell ref="U2:AR2"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
     <mergeCell ref="AK47:AR47"/>
     <mergeCell ref="AC48:AJ48"/>
     <mergeCell ref="AK48:AR48"/>
@@ -4988,6 +5017,19 @@
     <mergeCell ref="U48:AB48"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="B41:B42"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="AC47:AJ47"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A21:A24"/>
@@ -4996,34 +5038,6 @@
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="E4:L4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="AC3:AJ3"/>
-    <mergeCell ref="AC4:AJ4"/>
-    <mergeCell ref="AK3:AR3"/>
-    <mergeCell ref="AK4:AR4"/>
-    <mergeCell ref="U2:AR2"/>
-    <mergeCell ref="M4:T4"/>
-    <mergeCell ref="U4:AB4"/>
-    <mergeCell ref="M3:T3"/>
-    <mergeCell ref="U3:AB3"/>
-    <mergeCell ref="M2:T2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="E3:E4">
